--- a/Test Evidance/MSME/MSM_total_valid_records_566094.xlsx
+++ b/Test Evidance/MSME/MSM_total_valid_records_566094.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet3 (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="164">
   <si>
     <t>New CG</t>
   </si>
@@ -139,6 +140,12 @@
     <t>GuaranteeIssueEndDate</t>
   </si>
   <si>
+    <t>refund</t>
+  </si>
+  <si>
+    <t>Total Refund</t>
+  </si>
+  <si>
     <t>KUMAR</t>
   </si>
   <si>
@@ -431,6 +438,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Total CG Fees Received in the Previous Year column </t>
     </r>
     <r>
@@ -460,13 +473,13 @@
     <t>As checked with CGMSMGEN2209202600357171 CGfee in previous FY is showing as 491095.89 (excluding initial contribution)  ---&gt; Need to recheck this with peeyush sir</t>
   </si>
   <si>
+    <t>Resolved</t>
+  </si>
+  <si>
     <t>Maximum Claim Limit for the current FY should be three times the CG Fee and Recovery, instead of twice.</t>
   </si>
   <si>
     <t>As per the BRD, it is mentioned as twice.</t>
-  </si>
-  <si>
-    <t>Resolved</t>
   </si>
   <si>
     <t>If the OTS date is less than one year from the Legal Action Date, an error is displayed, but the system still allows claim submission.</t>
@@ -527,18 +540,31 @@
   <si>
     <t>https://prnt.sc/tCYdrsxOdtws
 https://prnt.sc/8Ek7kjfUMRvb</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Implemented changes</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Need discussion</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="181" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -728,6 +754,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -736,12 +768,6 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1220,15 +1246,24 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1237,18 +1272,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1301,181 +1335,187 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="108">
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
+  <dxfs count="110">
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <fill>
@@ -1950,25 +1990,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="97"/>
-      <tableStyleElement type="headerRow" dxfId="96"/>
-      <tableStyleElement type="totalRow" dxfId="95"/>
-      <tableStyleElement type="firstColumn" dxfId="94"/>
-      <tableStyleElement type="lastColumn" dxfId="93"/>
-      <tableStyleElement type="firstRowStripe" dxfId="92"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="91"/>
+      <tableStyleElement type="wholeTable" dxfId="99"/>
+      <tableStyleElement type="headerRow" dxfId="98"/>
+      <tableStyleElement type="totalRow" dxfId="97"/>
+      <tableStyleElement type="firstColumn" dxfId="96"/>
+      <tableStyleElement type="lastColumn" dxfId="95"/>
+      <tableStyleElement type="firstRowStripe" dxfId="94"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="93"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="107"/>
-      <tableStyleElement type="totalRow" dxfId="106"/>
-      <tableStyleElement type="firstRowStripe" dxfId="105"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="104"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="103"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="102"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="101"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="100"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="99"/>
-      <tableStyleElement type="pageFieldValues" dxfId="98"/>
+      <tableStyleElement type="headerRow" dxfId="109"/>
+      <tableStyleElement type="totalRow" dxfId="108"/>
+      <tableStyleElement type="firstRowStripe" dxfId="107"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="106"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="105"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="104"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="103"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="102"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="101"/>
+      <tableStyleElement type="pageFieldValues" dxfId="100"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1980,9 +2020,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:AI14" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AI14" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:AK14" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AK14" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="37">
     <tableColumn id="1" name="UnitName" dataDxfId="0"/>
     <tableColumn id="2" name="EmailId" dataDxfId="1"/>
     <tableColumn id="3" name="MobileNo" dataDxfId="2"/>
@@ -2018,6 +2064,12 @@
     <tableColumn id="33" name="IGST" dataDxfId="32"/>
     <tableColumn id="34" name="GuaranteeIssueStartDate" dataDxfId="33"/>
     <tableColumn id="35" name="GuaranteeIssueEndDate" dataDxfId="34"/>
+    <tableColumn id="36" name="refund" dataDxfId="35">
+      <calculatedColumnFormula>1%*AD3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="37" name="Total Refund" dataDxfId="36">
+      <calculatedColumnFormula>IF(T3=1,5%*AD3,2%*AD3)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2027,14 +2079,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table1_3" displayName="Table1_3" ref="A18:H30" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A18:H30" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="CGPAN" dataDxfId="35"/>
-    <tableColumn id="2" name="LoanAccountNumber" dataDxfId="36"/>
-    <tableColumn id="3" name="DisbursementAmount" dataDxfId="37"/>
-    <tableColumn id="4" name="DisbursementDate" dataDxfId="38"/>
-    <tableColumn id="5" name="CGFees" dataDxfId="39"/>
-    <tableColumn id="6" name="IGST" dataDxfId="40"/>
-    <tableColumn id="7" name="CGST" dataDxfId="41"/>
-    <tableColumn id="8" name="SGST" dataDxfId="42"/>
+    <tableColumn id="1" name="CGPAN" dataDxfId="37"/>
+    <tableColumn id="2" name="LoanAccountNumber" dataDxfId="38"/>
+    <tableColumn id="3" name="DisbursementAmount" dataDxfId="39"/>
+    <tableColumn id="4" name="DisbursementDate" dataDxfId="40"/>
+    <tableColumn id="5" name="CGFees" dataDxfId="41"/>
+    <tableColumn id="6" name="IGST" dataDxfId="42"/>
+    <tableColumn id="7" name="CGST" dataDxfId="43"/>
+    <tableColumn id="8" name="SGST" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2044,20 +2096,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table1_4" displayName="Table1_4" ref="A34:N46" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A34:N46" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="43"/>
-    <tableColumn id="2" name="CGPAN" dataDxfId="44"/>
-    <tableColumn id="3" name="PrincipalOutstandingAmount" dataDxfId="45"/>
-    <tableColumn id="4" name="InterestOutstandingAmount" dataDxfId="46"/>
-    <tableColumn id="5" name="AccountType" dataDxfId="47"/>
-    <tableColumn id="6" name="AccountTurnDate" dataDxfId="48"/>
-    <tableColumn id="7" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="49"/>
-    <tableColumn id="8" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="50"/>
-    <tableColumn id="9" name="CGFees" dataDxfId="51"/>
-    <tableColumn id="10" name="CGST" dataDxfId="52"/>
-    <tableColumn id="11" name="SGST" dataDxfId="53"/>
-    <tableColumn id="12" name="IGST" dataDxfId="54"/>
-    <tableColumn id="13" name="GuaranteeIssueStartDate" dataDxfId="55"/>
-    <tableColumn id="14" name="GuaranteeIssueEndDate" dataDxfId="56"/>
+    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="45"/>
+    <tableColumn id="2" name="CGPAN" dataDxfId="46"/>
+    <tableColumn id="3" name="PrincipalOutstandingAmount" dataDxfId="47"/>
+    <tableColumn id="4" name="InterestOutstandingAmount" dataDxfId="48"/>
+    <tableColumn id="5" name="AccountType" dataDxfId="49"/>
+    <tableColumn id="6" name="AccountTurnDate" dataDxfId="50"/>
+    <tableColumn id="7" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="51"/>
+    <tableColumn id="8" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="52"/>
+    <tableColumn id="9" name="CGFees" dataDxfId="53"/>
+    <tableColumn id="10" name="CGST" dataDxfId="54"/>
+    <tableColumn id="11" name="SGST" dataDxfId="55"/>
+    <tableColumn id="12" name="IGST" dataDxfId="56"/>
+    <tableColumn id="13" name="GuaranteeIssueStartDate" dataDxfId="57"/>
+    <tableColumn id="14" name="GuaranteeIssueEndDate" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2067,14 +2119,14 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table1_5" displayName="Table1_5" ref="J18:Q30" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="J18:Q30" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="CGPAN" dataDxfId="57"/>
-    <tableColumn id="2" name="LoanAccountNumber" dataDxfId="58"/>
-    <tableColumn id="3" name="DisbursementAmount" dataDxfId="59"/>
-    <tableColumn id="4" name="DisbursementDate" dataDxfId="60"/>
-    <tableColumn id="5" name="CGFees" dataDxfId="61"/>
-    <tableColumn id="6" name="IGST" dataDxfId="62"/>
-    <tableColumn id="7" name="CGST" dataDxfId="63"/>
-    <tableColumn id="8" name="SGST" dataDxfId="64"/>
+    <tableColumn id="1" name="CGPAN" dataDxfId="59"/>
+    <tableColumn id="2" name="LoanAccountNumber" dataDxfId="60"/>
+    <tableColumn id="3" name="DisbursementAmount" dataDxfId="61"/>
+    <tableColumn id="4" name="DisbursementDate" dataDxfId="62"/>
+    <tableColumn id="5" name="CGFees" dataDxfId="63"/>
+    <tableColumn id="6" name="IGST" dataDxfId="64"/>
+    <tableColumn id="7" name="CGST" dataDxfId="65"/>
+    <tableColumn id="8" name="SGST" dataDxfId="66"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2082,28 +2134,22 @@
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table1_6" displayName="Table1_6" ref="A50:N62" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A50:N62" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="CGMSMGEN2209202600357171"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A50:N62" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="65"/>
-    <tableColumn id="2" name="CGPAN" dataDxfId="66"/>
-    <tableColumn id="3" name="PrincipalOutstandingAmount" dataDxfId="67"/>
-    <tableColumn id="4" name="InterestOutstandingAmount" dataDxfId="68"/>
-    <tableColumn id="5" name="AccountType" dataDxfId="69"/>
-    <tableColumn id="6" name="AccountTurnDate" dataDxfId="70"/>
-    <tableColumn id="7" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="71"/>
-    <tableColumn id="8" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="72"/>
-    <tableColumn id="9" name="CGFees" dataDxfId="73"/>
-    <tableColumn id="10" name="CGST" dataDxfId="74"/>
-    <tableColumn id="11" name="SGST" dataDxfId="75"/>
-    <tableColumn id="12" name="IGST" dataDxfId="76"/>
-    <tableColumn id="13" name="GuaranteeIssueStartDate" dataDxfId="77"/>
-    <tableColumn id="14" name="GuaranteeIssueEndDate" dataDxfId="78"/>
+    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="67"/>
+    <tableColumn id="2" name="CGPAN" dataDxfId="68"/>
+    <tableColumn id="3" name="PrincipalOutstandingAmount" dataDxfId="69"/>
+    <tableColumn id="4" name="InterestOutstandingAmount" dataDxfId="70"/>
+    <tableColumn id="5" name="AccountType" dataDxfId="71"/>
+    <tableColumn id="6" name="AccountTurnDate" dataDxfId="72"/>
+    <tableColumn id="7" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="73"/>
+    <tableColumn id="8" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="74"/>
+    <tableColumn id="9" name="CGFees" dataDxfId="75"/>
+    <tableColumn id="10" name="CGST" dataDxfId="76"/>
+    <tableColumn id="11" name="SGST" dataDxfId="77"/>
+    <tableColumn id="12" name="IGST" dataDxfId="78"/>
+    <tableColumn id="13" name="GuaranteeIssueStartDate" dataDxfId="79"/>
+    <tableColumn id="14" name="GuaranteeIssueEndDate" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2113,18 +2159,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table1_7" displayName="Table1_7" ref="A66:L68" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A66:L68" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="12">
-    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="79"/>
-    <tableColumn id="2" name="CGPAN" dataDxfId="80"/>
-    <tableColumn id="3" name="AccountType" dataDxfId="81"/>
-    <tableColumn id="4" name="AccountTurnDate" dataDxfId="82"/>
-    <tableColumn id="5" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="83"/>
-    <tableColumn id="6" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="84"/>
-    <tableColumn id="7" name="CGFees" dataDxfId="85"/>
-    <tableColumn id="8" name="CGST" dataDxfId="86"/>
-    <tableColumn id="9" name="SGST" dataDxfId="87"/>
-    <tableColumn id="10" name="IGST" dataDxfId="88"/>
-    <tableColumn id="11" name="GuaranteeIssueStartDate" dataDxfId="89"/>
-    <tableColumn id="12" name="GuaranteeIssueEndDate" dataDxfId="90"/>
+    <tableColumn id="1" name="LoanAccountNumber" dataDxfId="81"/>
+    <tableColumn id="2" name="CGPAN" dataDxfId="82"/>
+    <tableColumn id="3" name="AccountType" dataDxfId="83"/>
+    <tableColumn id="4" name="AccountTurnDate" dataDxfId="84"/>
+    <tableColumn id="5" name="PrincipalOutstandingAmountAsOnNPADate" dataDxfId="85"/>
+    <tableColumn id="6" name="InterestOutstandingAmountAsOnNPADate" dataDxfId="86"/>
+    <tableColumn id="7" name="CGFees" dataDxfId="87"/>
+    <tableColumn id="8" name="CGST" dataDxfId="88"/>
+    <tableColumn id="9" name="SGST" dataDxfId="89"/>
+    <tableColumn id="10" name="IGST" dataDxfId="90"/>
+    <tableColumn id="11" name="GuaranteeIssueStartDate" dataDxfId="91"/>
+    <tableColumn id="12" name="GuaranteeIssueEndDate" dataDxfId="92"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2415,7 +2461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI68"/>
+  <dimension ref="A1:AK68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.8571428571429" customWidth="1"/>
@@ -2453,20 +2499,21 @@
     <col min="33" max="33" width="6.83809523809524" customWidth="1"/>
     <col min="34" max="34" width="25.1333333333333" customWidth="1"/>
     <col min="35" max="35" width="24.2666666666667" customWidth="1"/>
+    <col min="37" max="37" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
-      <c r="A1" s="8">
+    <row r="1" spans="1:37">
+      <c r="A1" s="11">
         <v>46287</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10">
+      <c r="B1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:35">
+    <row r="2" spans="1:37">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2572,49 +2619,55 @@
       <c r="AI2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:35">
+      <c r="AJ2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" hidden="1" spans="1:37">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3">
         <v>3</v>
@@ -2622,44 +2675,44 @@
       <c r="P3">
         <v>300000000</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="13">
         <v>46199</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z3">
         <v>50000000</v>
       </c>
       <c r="AA3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AD3">
         <v>12500000</v>
@@ -2673,55 +2726,63 @@
       <c r="AG3">
         <v>0</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AH3" s="13">
         <v>46287</v>
       </c>
-      <c r="AI3" s="11">
+      <c r="AI3" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="4" spans="1:35">
+      <c r="AJ3" s="14">
+        <f t="shared" ref="AJ3:AJ14" si="0">1%*AD3</f>
+        <v>125000</v>
+      </c>
+      <c r="AK3" s="14">
+        <f t="shared" ref="AK3:AK14" si="1">IF(T3=1,5%*AD3,2%*AD3)</f>
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="4" hidden="1" spans="1:37">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -2729,44 +2790,44 @@
       <c r="P4">
         <v>1000000000</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="13">
         <v>46199</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T4">
         <v>1</v>
       </c>
       <c r="U4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z4">
         <v>450000000</v>
       </c>
       <c r="AA4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AD4">
         <v>27500000</v>
@@ -2780,55 +2841,63 @@
       <c r="AG4">
         <v>0</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AH4" s="13">
         <v>46287</v>
       </c>
-      <c r="AI4" s="11">
+      <c r="AI4" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="5" spans="1:35">
+      <c r="AJ4" s="14">
+        <f t="shared" si="0"/>
+        <v>275000</v>
+      </c>
+      <c r="AK4" s="14">
+        <f t="shared" si="1"/>
+        <v>1375000</v>
+      </c>
+    </row>
+    <row r="5" hidden="1" spans="1:37">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O5">
         <v>11</v>
@@ -2836,44 +2905,44 @@
       <c r="P5">
         <v>500000000</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="Q5" s="13">
         <v>46199</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T5">
         <v>1</v>
       </c>
       <c r="U5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z5">
         <v>150000000</v>
       </c>
       <c r="AA5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AD5">
         <v>17500000</v>
@@ -2887,55 +2956,63 @@
       <c r="AG5">
         <v>0</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AH5" s="13">
         <v>46287</v>
       </c>
-      <c r="AI5" s="11">
+      <c r="AI5" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="6" spans="1:35">
+      <c r="AJ5" s="14">
+        <f t="shared" si="0"/>
+        <v>175000</v>
+      </c>
+      <c r="AK5" s="14">
+        <f t="shared" si="1"/>
+        <v>875000</v>
+      </c>
+    </row>
+    <row r="6" hidden="1" spans="1:37">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O6">
         <v>11</v>
@@ -2943,44 +3020,44 @@
       <c r="P6">
         <v>500000000</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="Q6" s="13">
         <v>46199</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="U6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z6">
         <v>450000000</v>
       </c>
       <c r="AA6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD6">
         <v>2500000</v>
@@ -2994,55 +3071,63 @@
       <c r="AG6">
         <v>0</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AH6" s="13">
         <v>46287</v>
       </c>
-      <c r="AI6" s="11">
+      <c r="AI6" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="7" spans="1:35">
+      <c r="AJ6" s="14">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="AK6" s="14">
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="7" hidden="1" spans="1:37">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O7">
         <v>11</v>
@@ -3050,44 +3135,44 @@
       <c r="P7">
         <v>600000000</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="Q7" s="13">
         <v>46199</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T7">
         <v>1</v>
       </c>
       <c r="U7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z7">
         <v>0</v>
       </c>
       <c r="AA7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AD7">
         <v>30000000</v>
@@ -3101,55 +3186,63 @@
       <c r="AG7">
         <v>0</v>
       </c>
-      <c r="AH7" s="11">
+      <c r="AH7" s="13">
         <v>46287</v>
       </c>
-      <c r="AI7" s="11">
+      <c r="AI7" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="8" spans="1:35">
+      <c r="AJ7" s="14">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
+      <c r="AK7" s="14">
+        <f t="shared" si="1"/>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="8" hidden="1" spans="1:37">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O8">
         <v>11</v>
@@ -3157,44 +3250,44 @@
       <c r="P8">
         <v>500000000</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="Q8" s="13">
         <v>46199</v>
       </c>
       <c r="R8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T8">
         <v>1</v>
       </c>
       <c r="U8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z8">
         <v>450000000</v>
       </c>
       <c r="AA8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AD8">
         <v>2500000</v>
@@ -3208,55 +3301,63 @@
       <c r="AG8">
         <v>0</v>
       </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="13">
         <v>46287</v>
       </c>
-      <c r="AI8" s="11">
+      <c r="AI8" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="9" spans="1:35">
+      <c r="AJ8" s="14">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+      <c r="AK8" s="14">
+        <f t="shared" si="1"/>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O9">
         <v>11</v>
@@ -3264,44 +3365,44 @@
       <c r="P9">
         <v>200000000</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="Q9" s="13">
         <v>46199</v>
       </c>
       <c r="R9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T9">
         <v>2</v>
       </c>
       <c r="U9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z9">
         <v>50000000</v>
       </c>
       <c r="AA9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AD9">
         <v>3000000</v>
@@ -3315,55 +3416,63 @@
       <c r="AG9">
         <v>0</v>
       </c>
-      <c r="AH9" s="11">
+      <c r="AH9" s="13">
         <v>46287</v>
       </c>
-      <c r="AI9" s="11">
+      <c r="AI9" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="10" spans="1:35">
+      <c r="AJ9" s="14">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="AK9" s="14">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O10">
         <v>11</v>
@@ -3371,41 +3480,41 @@
       <c r="P10">
         <v>100000000</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="Q10" s="13">
         <v>46199</v>
       </c>
       <c r="R10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T10">
         <v>2</v>
       </c>
       <c r="U10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z10">
         <v>50000000</v>
       </c>
       <c r="AA10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC10" t="s">
         <v>30</v>
@@ -3422,55 +3531,63 @@
       <c r="AG10">
         <v>0</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AH10" s="13">
         <v>46287</v>
       </c>
-      <c r="AI10" s="11">
+      <c r="AI10" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="11" spans="1:35">
+      <c r="AJ10" s="14">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="AK10" s="14">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O11">
         <v>11</v>
@@ -3478,44 +3595,44 @@
       <c r="P11">
         <v>150000000</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="13">
         <v>46199</v>
       </c>
       <c r="R11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T11">
         <v>2</v>
       </c>
       <c r="U11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z11">
         <v>50000000</v>
       </c>
       <c r="AA11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AD11">
         <v>2000000</v>
@@ -3529,55 +3646,63 @@
       <c r="AG11">
         <v>0</v>
       </c>
-      <c r="AH11" s="11">
+      <c r="AH11" s="13">
         <v>46287</v>
       </c>
-      <c r="AI11" s="11">
+      <c r="AI11" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="12" spans="1:35">
+      <c r="AJ11" s="14">
+        <f t="shared" si="0"/>
+        <v>20000</v>
+      </c>
+      <c r="AK11" s="14">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O12">
         <v>11</v>
@@ -3585,44 +3710,44 @@
       <c r="P12">
         <v>100000000</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="13">
         <v>46199</v>
       </c>
       <c r="R12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T12">
         <v>2</v>
       </c>
       <c r="U12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z12">
         <v>50000000</v>
       </c>
       <c r="AA12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AD12">
         <v>1000000</v>
@@ -3636,55 +3761,63 @@
       <c r="AG12">
         <v>0</v>
       </c>
-      <c r="AH12" s="11">
+      <c r="AH12" s="13">
         <v>46287</v>
       </c>
-      <c r="AI12" s="11">
+      <c r="AI12" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="13" spans="1:35">
+      <c r="AJ12" s="14">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="AK12" s="14">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O13">
         <v>11</v>
@@ -3692,44 +3825,44 @@
       <c r="P13">
         <v>180000000</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="13">
         <v>46199</v>
       </c>
       <c r="R13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T13">
         <v>2</v>
       </c>
       <c r="U13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z13">
         <v>50000000</v>
       </c>
       <c r="AA13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AD13">
         <v>2600000</v>
@@ -3743,55 +3876,63 @@
       <c r="AG13">
         <v>0</v>
       </c>
-      <c r="AH13" s="11">
+      <c r="AH13" s="13">
         <v>46287</v>
       </c>
-      <c r="AI13" s="11">
+      <c r="AI13" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="14" spans="1:35">
+      <c r="AJ13" s="14">
+        <f t="shared" si="0"/>
+        <v>26000</v>
+      </c>
+      <c r="AK13" s="14">
+        <f t="shared" si="1"/>
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O14">
         <v>11</v>
@@ -3799,44 +3940,44 @@
       <c r="P14">
         <v>20000000</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="13">
         <v>46199</v>
       </c>
       <c r="R14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="T14">
         <v>2</v>
       </c>
       <c r="U14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="V14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="W14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z14">
         <v>0</v>
       </c>
       <c r="AA14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AB14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AD14">
         <v>400000</v>
@@ -3850,34 +3991,42 @@
       <c r="AG14">
         <v>0</v>
       </c>
-      <c r="AH14" s="11">
+      <c r="AH14" s="13">
         <v>46287</v>
       </c>
-      <c r="AI14" s="11">
+      <c r="AI14" s="13">
         <v>46477</v>
       </c>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="8">
+      <c r="AJ14" s="14">
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="AK14" s="14">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34">
+      <c r="A17" s="11">
         <v>46287</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="10">
+      <c r="B17" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="12">
         <v>2</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="11">
         <v>46487</v>
       </c>
-      <c r="K17" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="10">
+      <c r="K17" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:34">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -3885,13 +4034,13 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
         <v>33</v>
@@ -3909,13 +4058,13 @@
         <v>14</v>
       </c>
       <c r="L18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O18" t="s">
         <v>33</v>
@@ -3927,18 +4076,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3953,16 +4102,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M19" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N19">
         <v>3616438.35</v>
@@ -3976,19 +4125,20 @@
       <c r="Q19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:17">
+      <c r="AH19" s="15"/>
+    </row>
+    <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4003,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K20" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N20">
         <v>7956164.37</v>
@@ -4027,42 +4177,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" t="s">
         <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>66</v>
-      </c>
-      <c r="K21" t="s">
-        <v>65</v>
-      </c>
-      <c r="L21" t="s">
-        <v>53</v>
-      </c>
-      <c r="M21" t="s">
-        <v>102</v>
       </c>
       <c r="N21">
         <v>5063013.69</v>
@@ -4077,42 +4227,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>72</v>
+      </c>
+      <c r="K22" t="s">
+        <v>71</v>
+      </c>
+      <c r="L22" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" t="s">
         <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" t="s">
-        <v>69</v>
-      </c>
-      <c r="L22" t="s">
-        <v>53</v>
-      </c>
-      <c r="M22" t="s">
-        <v>102</v>
       </c>
       <c r="N22">
         <v>723287.67</v>
@@ -4127,42 +4277,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L23" t="s">
+        <v>106</v>
+      </c>
+      <c r="M23" t="s">
         <v>104</v>
-      </c>
-      <c r="D23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>74</v>
-      </c>
-      <c r="K23" t="s">
-        <v>73</v>
-      </c>
-      <c r="L23" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23" t="s">
-        <v>102</v>
       </c>
       <c r="N23">
         <v>8679452.04</v>
@@ -4177,18 +4327,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4203,16 +4353,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N24">
         <v>723287.67</v>
@@ -4227,18 +4377,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4253,16 +4403,16 @@
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L25" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M25" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N25">
         <v>723287.67</v>
@@ -4277,18 +4427,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:34">
       <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4306,13 +4456,13 @@
         <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L26" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N26">
         <v>241095.89</v>
@@ -4327,18 +4477,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4353,16 +4503,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N27">
         <v>482191.78</v>
@@ -4377,18 +4527,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4403,16 +4553,16 @@
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N28">
         <v>241095.89</v>
@@ -4427,18 +4577,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4453,16 +4603,16 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N29">
         <v>626849.31</v>
@@ -4477,18 +4627,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4503,16 +4653,16 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N30">
         <v>96438.36</v>
@@ -4528,13 +4678,13 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="8">
+      <c r="A33" s="11">
         <v>46487</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="10">
+      <c r="B33" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="12">
         <v>3</v>
       </c>
     </row>
@@ -4546,25 +4696,25 @@
         <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J34" t="s">
         <v>31</v>
@@ -4584,10 +4734,10 @@
     </row>
     <row r="35" customFormat="1" spans="1:14">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>200000000</v>
@@ -4596,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I35">
         <v>2250000</v>
@@ -4610,19 +4760,19 @@
       <c r="L35">
         <v>405000</v>
       </c>
-      <c r="M35" s="11">
+      <c r="M35" s="13">
         <v>46478</v>
       </c>
-      <c r="N35" s="11">
+      <c r="N35" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:14">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>500000000</v>
@@ -4631,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I36">
         <v>750000</v>
@@ -4645,19 +4795,19 @@
       <c r="L36">
         <v>135000</v>
       </c>
-      <c r="M36" s="11">
+      <c r="M36" s="13">
         <v>46478</v>
       </c>
-      <c r="N36" s="11">
+      <c r="N36" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:14">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C37">
         <v>300000000</v>
@@ -4666,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I37">
         <v>2250000</v>
@@ -4680,19 +4830,19 @@
       <c r="L37">
         <v>405000</v>
       </c>
-      <c r="M37" s="11">
+      <c r="M37" s="13">
         <v>46478</v>
       </c>
-      <c r="N37" s="11">
+      <c r="N37" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:14">
       <c r="A38" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38">
         <v>300000000</v>
@@ -4701,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4715,19 +4865,19 @@
       <c r="L38">
         <v>0</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="13">
         <v>46478</v>
       </c>
-      <c r="N38" s="11">
+      <c r="N38" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:14">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C39">
         <v>300000000</v>
@@ -4736,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I39">
         <v>4500000</v>
@@ -4750,19 +4900,19 @@
       <c r="L39">
         <v>810000</v>
       </c>
-      <c r="M39" s="11">
+      <c r="M39" s="13">
         <v>46478</v>
       </c>
-      <c r="N39" s="11">
+      <c r="N39" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:14">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40">
         <v>460000000</v>
@@ -4771,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I40">
         <v>150000</v>
@@ -4785,19 +4935,19 @@
       <c r="L40">
         <v>27000</v>
       </c>
-      <c r="M40" s="11">
+      <c r="M40" s="13">
         <v>46478</v>
       </c>
-      <c r="N40" s="11">
+      <c r="N40" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:14">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>100000000</v>
@@ -4806,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I41">
         <v>250000</v>
@@ -4820,16 +4970,16 @@
       <c r="L41">
         <v>45000</v>
       </c>
-      <c r="M41" s="11">
+      <c r="M41" s="13">
         <v>46478</v>
       </c>
-      <c r="N41" s="11">
+      <c r="N41" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:14">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
         <v>30</v>
@@ -4841,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I42">
         <v>250000</v>
@@ -4855,19 +5005,19 @@
       <c r="L42">
         <v>45000</v>
       </c>
-      <c r="M42" s="11">
+      <c r="M42" s="13">
         <v>46478</v>
       </c>
-      <c r="N42" s="11">
+      <c r="N42" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:14">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C43">
         <v>100000000</v>
@@ -4876,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I43">
         <v>250000</v>
@@ -4890,19 +5040,19 @@
       <c r="L43">
         <v>45000</v>
       </c>
-      <c r="M43" s="11">
+      <c r="M43" s="13">
         <v>46478</v>
       </c>
-      <c r="N43" s="11">
+      <c r="N43" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:14">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C44">
         <v>100000000</v>
@@ -4911,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I44">
         <v>250000</v>
@@ -4925,19 +5075,19 @@
       <c r="L44">
         <v>45000</v>
       </c>
-      <c r="M44" s="11">
+      <c r="M44" s="13">
         <v>46478</v>
       </c>
-      <c r="N44" s="11">
+      <c r="N44" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:14">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C45">
         <v>100000000</v>
@@ -4946,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I45">
         <v>250000</v>
@@ -4960,19 +5110,19 @@
       <c r="L45">
         <v>45000</v>
       </c>
-      <c r="M45" s="11">
+      <c r="M45" s="13">
         <v>46478</v>
       </c>
-      <c r="N45" s="11">
+      <c r="N45" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:14">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46">
         <v>10000000</v>
@@ -4981,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I46">
         <v>50000</v>
@@ -4995,21 +5145,21 @@
       <c r="L46">
         <v>9000</v>
       </c>
-      <c r="M46" s="11">
+      <c r="M46" s="13">
         <v>46478</v>
       </c>
-      <c r="N46" s="11">
+      <c r="N46" s="13">
         <v>46843</v>
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="8">
+      <c r="A49" s="11">
         <v>46844</v>
       </c>
-      <c r="B49" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" s="9">
+      <c r="B49" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="12">
         <v>5</v>
       </c>
     </row>
@@ -5021,25 +5171,25 @@
         <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G50" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s">
         <v>31</v>
@@ -5057,12 +5207,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" customFormat="1" hidden="1" spans="1:14">
+    <row r="51" customFormat="1" spans="1:14">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C51">
         <v>300000000</v>
@@ -5071,10 +5221,10 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G51">
         <v>300000000</v>
@@ -5094,19 +5244,19 @@
       <c r="L51">
         <v>0</v>
       </c>
-      <c r="M51" s="11">
+      <c r="M51" s="13">
         <v>46844</v>
       </c>
-      <c r="N51" s="11">
+      <c r="N51" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="52" customFormat="1" hidden="1" spans="1:14">
+    <row r="52" customFormat="1" spans="1:14">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C52">
         <v>1000000000</v>
@@ -5115,10 +5265,10 @@
         <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G52">
         <v>1000000000</v>
@@ -5138,19 +5288,19 @@
       <c r="L52">
         <v>0</v>
       </c>
-      <c r="M52" s="11">
+      <c r="M52" s="13">
         <v>46844</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="53" customFormat="1" hidden="1" spans="1:14">
+    <row r="53" customFormat="1" spans="1:14">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C53">
         <v>500000000</v>
@@ -5159,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G53">
         <v>500000000</v>
@@ -5182,19 +5332,19 @@
       <c r="L53">
         <v>0</v>
       </c>
-      <c r="M53" s="11">
+      <c r="M53" s="13">
         <v>46844</v>
       </c>
-      <c r="N53" s="11">
+      <c r="N53" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="54" customFormat="1" hidden="1" spans="1:14">
+    <row r="54" customFormat="1" spans="1:14">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C54">
         <v>500000000</v>
@@ -5203,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I54">
         <v>750000</v>
@@ -5217,19 +5367,19 @@
       <c r="L54">
         <v>135000</v>
       </c>
-      <c r="M54" s="11">
+      <c r="M54" s="13">
         <v>46844</v>
       </c>
-      <c r="N54" s="11">
+      <c r="N54" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="55" customFormat="1" hidden="1" spans="1:14">
+    <row r="55" customFormat="1" spans="1:14">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>600000000</v>
@@ -5238,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I55">
         <v>9000000</v>
@@ -5252,19 +5402,19 @@
       <c r="L55">
         <v>1620000</v>
       </c>
-      <c r="M55" s="11">
+      <c r="M55" s="13">
         <v>46844</v>
       </c>
-      <c r="N55" s="11">
+      <c r="N55" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="56" customFormat="1" hidden="1" spans="1:14">
+    <row r="56" customFormat="1" spans="1:14">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>500000000</v>
@@ -5273,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I56">
         <v>750000</v>
@@ -5287,19 +5437,19 @@
       <c r="L56">
         <v>135000</v>
       </c>
-      <c r="M56" s="11">
+      <c r="M56" s="13">
         <v>46844</v>
       </c>
-      <c r="N56" s="11">
+      <c r="N56" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="57" customFormat="1" hidden="1" spans="1:14">
+    <row r="57" customFormat="1" spans="1:14">
       <c r="A57" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C57">
         <v>200000000</v>
@@ -5308,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I57">
         <v>750000</v>
@@ -5322,16 +5472,16 @@
       <c r="L57">
         <v>135000</v>
       </c>
-      <c r="M57" s="11">
+      <c r="M57" s="13">
         <v>46844</v>
       </c>
-      <c r="N57" s="11">
+      <c r="N57" s="13">
         <v>47208</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:14">
       <c r="A58" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
         <v>30</v>
@@ -5343,10 +5493,10 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F58" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G58">
         <v>10000000</v>
@@ -5366,19 +5516,19 @@
       <c r="L58">
         <v>0</v>
       </c>
-      <c r="M58" s="11">
+      <c r="M58" s="13">
         <v>46844</v>
       </c>
-      <c r="N58" s="11">
+      <c r="N58" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="59" customFormat="1" hidden="1" spans="1:14">
+    <row r="59" customFormat="1" spans="1:14">
       <c r="A59" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C59">
         <v>150000000</v>
@@ -5387,10 +5537,10 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F59" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G59">
         <v>50000000</v>
@@ -5410,19 +5560,19 @@
       <c r="L59">
         <v>0</v>
       </c>
-      <c r="M59" s="11">
+      <c r="M59" s="13">
         <v>46844</v>
       </c>
-      <c r="N59" s="11">
+      <c r="N59" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="60" customFormat="1" hidden="1" spans="1:14">
+    <row r="60" customFormat="1" spans="1:14">
       <c r="A60" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>100000000</v>
@@ -5431,10 +5581,10 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F60" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G60">
         <v>10000000</v>
@@ -5454,19 +5604,19 @@
       <c r="L60">
         <v>0</v>
       </c>
-      <c r="M60" s="11">
+      <c r="M60" s="13">
         <v>46844</v>
       </c>
-      <c r="N60" s="11">
+      <c r="N60" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="61" customFormat="1" hidden="1" spans="1:14">
+    <row r="61" customFormat="1" spans="1:14">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C61">
         <v>180000000</v>
@@ -5475,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I61">
         <v>650000</v>
@@ -5489,19 +5639,19 @@
       <c r="L61">
         <v>117000</v>
       </c>
-      <c r="M61" s="11">
+      <c r="M61" s="13">
         <v>46844</v>
       </c>
-      <c r="N61" s="11">
+      <c r="N61" s="13">
         <v>47208</v>
       </c>
     </row>
-    <row r="62" customFormat="1" hidden="1" spans="1:14">
+    <row r="62" customFormat="1" spans="1:14">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C62">
         <v>20000000</v>
@@ -5510,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I62">
         <v>100000</v>
@@ -5524,21 +5674,21 @@
       <c r="L62">
         <v>18000</v>
       </c>
-      <c r="M62" s="11">
+      <c r="M62" s="13">
         <v>46844</v>
       </c>
-      <c r="N62" s="11">
+      <c r="N62" s="13">
         <v>47208</v>
       </c>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="8">
+      <c r="A65" s="11">
         <v>46914</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C65" s="9">
+      <c r="B65" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C65" s="12">
         <v>6</v>
       </c>
     </row>
@@ -5550,19 +5700,19 @@
         <v>29</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F66" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G66" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H66" t="s">
         <v>31</v>
@@ -5582,16 +5732,16 @@
     </row>
     <row r="67" customFormat="1" spans="1:12">
       <c r="A67" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E67">
         <v>500000000</v>
@@ -5611,25 +5761,25 @@
       <c r="J67">
         <v>0</v>
       </c>
-      <c r="K67" s="11">
+      <c r="K67" s="13">
         <v>46844</v>
       </c>
-      <c r="L67" s="11">
+      <c r="L67" s="13">
         <v>47208</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:12">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E68">
         <v>100000000</v>
@@ -5649,10 +5799,10 @@
       <c r="J68">
         <v>0</v>
       </c>
-      <c r="K68" s="11">
+      <c r="K68" s="13">
         <v>46844</v>
       </c>
-      <c r="L68" s="11">
+      <c r="L68" s="13">
         <v>47208</v>
       </c>
     </row>
@@ -5674,8 +5824,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="7"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="19.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="35.1428571428571" customWidth="1"/>
@@ -5693,44 +5843,44 @@
       <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="E1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>128</v>
       </c>
+      <c r="G1" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="D2" s="7">
+      <c r="D2" s="10">
         <v>1000000</v>
       </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="E2" s="10">
+        <v>0</v>
+      </c>
+      <c r="F2" s="10">
         <v>250000</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="10">
         <v>241095.89</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>491095.89</v>
-      </c>
-      <c r="D4" s="7">
+        <v>579493.15</v>
+      </c>
+      <c r="D4" s="10">
         <v>1000000</v>
       </c>
       <c r="F4">
@@ -5738,6 +5888,11 @@
       </c>
       <c r="G4">
         <v>284493.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>14160000</v>
       </c>
     </row>
   </sheetData>
@@ -5749,150 +5904,165 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="58" customWidth="1"/>
     <col min="3" max="3" width="68.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="47" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="18.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="2" ht="75" spans="1:4">
-      <c r="A2" s="1">
+      <c r="C1" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" ht="45" spans="1:5">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="3" ht="45" spans="1:4">
-      <c r="A3" s="1">
+      <c r="C2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:5">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="4" ht="75" spans="1:4">
-      <c r="A4" s="1">
+      <c r="E3" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" ht="60" spans="1:5">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="5" ht="60" spans="1:4">
-      <c r="A5" s="1">
+      <c r="C4" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" ht="45" spans="1:5">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="6" ht="30" spans="1:4">
-      <c r="A6" s="1">
+      <c r="C5" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:5">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="7" ht="45" spans="1:4">
-      <c r="A7" s="1">
+      <c r="C6" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" ht="45" spans="1:5">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="8" ht="60" spans="1:4">
-      <c r="A8" s="1">
+      <c r="C7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" ht="60" spans="1:5">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" ht="45" spans="1:4">
-      <c r="A9" s="1">
+    </row>
+    <row r="9" ht="30" spans="1:5">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" ht="45" spans="1:4">
+      <c r="B9" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" ht="45" spans="1:5">
       <c r="B14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="5" t="s">
         <v>157</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5902,4 +6072,155 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="59.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="68.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="18.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" ht="30" spans="1:4">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:4">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:4">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" ht="45" spans="1:4">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" ht="30" spans="1:4">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" ht="30" spans="1:4">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" ht="45" spans="1:4">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" ht="30" spans="1:4">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" ht="30" spans="1:4">
+      <c r="B14" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Test Evidance/MSME/MSM_total_valid_records_566094.xlsx
+++ b/Test Evidance/MSME/MSM_total_valid_records_566094.xlsx
@@ -2021,13 +2021,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:AK14" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AK14" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="19">
-      <filters>
-        <filter val="2"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:AK14" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="37">
     <tableColumn id="1" name="UnitName" dataDxfId="0"/>
     <tableColumn id="2" name="EmailId" dataDxfId="1"/>
@@ -2466,8 +2460,8 @@
   <cols>
     <col min="1" max="1" width="13.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="32.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="12.9809523809524" customWidth="1"/>
-    <col min="4" max="4" width="13.7047619047619" customWidth="1"/>
+    <col min="3" max="3" width="21.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="19.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="12.552380952381" customWidth="1"/>
     <col min="6" max="6" width="23.4095238095238" customWidth="1"/>
     <col min="7" max="7" width="14.1333333333333" customWidth="1"/>
@@ -2475,7 +2469,7 @@
     <col min="9" max="9" width="13.8380952380952" customWidth="1"/>
     <col min="10" max="10" width="13.2857142857143" customWidth="1"/>
     <col min="11" max="11" width="10.1428571428571" customWidth="1"/>
-    <col min="12" max="12" width="7.55238095238095" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="10.4095238095238" customWidth="1"/>
     <col min="14" max="14" width="21.552380952381" customWidth="1"/>
     <col min="15" max="15" width="13.9809523809524" customWidth="1"/>
@@ -2626,7 +2620,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:37">
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -2741,7 +2735,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:37">
+    <row r="4" spans="1:37">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -2856,7 +2850,7 @@
         <v>1375000</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:37">
+    <row r="5" spans="1:37">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -2971,7 +2965,7 @@
         <v>875000</v>
       </c>
     </row>
-    <row r="6" hidden="1" spans="1:37">
+    <row r="6" spans="1:37">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -3086,7 +3080,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="7" hidden="1" spans="1:37">
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -3201,7 +3195,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:37">
+    <row r="8" spans="1:37">
       <c r="A8" t="s">
         <v>63</v>
       </c>
